--- a/W1_sdm_coef.xlsx
+++ b/W1_sdm_coef.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>变量</t>
   </si>
@@ -29,6 +29,15 @@
   </si>
   <si>
     <t>p值</t>
+  </si>
+  <si>
+    <t>稳健标准误(线性部分)</t>
+  </si>
+  <si>
+    <t>稳健z值(线性部分)</t>
+  </si>
+  <si>
+    <t>稳健p值(线性部分)</t>
   </si>
   <si>
     <t>rho</t>
@@ -422,10 +431,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -441,206 +450,305 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2">
-        <v>0.5904088881796419</v>
+        <v>0.5098381475967909</v>
       </c>
       <c r="C2">
-        <v>0.06681852770154456</v>
+        <v>0.06440949132956926</v>
       </c>
       <c r="D2">
-        <v>8.83600564826564</v>
+        <v>7.915574817817777</v>
       </c>
       <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>2.442490654175344E-15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3">
-        <v>0.003196602753312712</v>
+        <v>-0.01724369021140951</v>
       </c>
       <c r="C3">
-        <v>0.03289705857036083</v>
+        <v>0.0298193040095692</v>
       </c>
       <c r="D3">
-        <v>0.097169865399235</v>
+        <v>-0.5782727258113036</v>
       </c>
       <c r="E3">
-        <v>0.9225914987003971</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>0.5630800053018306</v>
+      </c>
+      <c r="F3">
+        <v>0.02543791287827343</v>
+      </c>
+      <c r="G3">
+        <v>-0.6778736248498353</v>
+      </c>
+      <c r="H3">
+        <v>0.4978518243408081</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4">
-        <v>-0.6283617097668415</v>
+        <v>-0.9153454355353468</v>
       </c>
       <c r="C4">
-        <v>0.3975158484769908</v>
+        <v>0.3634398698266714</v>
       </c>
       <c r="D4">
-        <v>-1.580721151557339</v>
+        <v>-2.518560872179174</v>
       </c>
       <c r="E4">
-        <v>0.1139418099119474</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>0.01178355133476794</v>
+      </c>
+      <c r="F4">
+        <v>0.3113518761975305</v>
+      </c>
+      <c r="G4">
+        <v>-2.939906599292903</v>
+      </c>
+      <c r="H4">
+        <v>0.003283111968687802</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B5">
-        <v>0.08555316398982532</v>
+        <v>0.05202813063913577</v>
       </c>
       <c r="C5">
-        <v>0.02442007298380735</v>
+        <v>0.01651493418371663</v>
       </c>
       <c r="D5">
-        <v>3.503395098227372</v>
+        <v>3.150368633647622</v>
       </c>
       <c r="E5">
-        <v>0.0004593675503783423</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>0.001630645705996026</v>
+      </c>
+      <c r="F5">
+        <v>0.01383478912495329</v>
+      </c>
+      <c r="G5">
+        <v>3.760673919148835</v>
+      </c>
+      <c r="H5">
+        <v>0.0001694562089471496</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B6">
-        <v>-0.8754426556135529</v>
+        <v>-0.8062778165745353</v>
       </c>
       <c r="C6">
-        <v>1.363166516599033</v>
+        <v>1.247623187901248</v>
       </c>
       <c r="D6">
-        <v>-0.6422125580062638</v>
+        <v>-0.6462510671438033</v>
       </c>
       <c r="E6">
-        <v>0.5207351802886551</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>0.5181167721978739</v>
+      </c>
+      <c r="F6">
+        <v>1.121737781278421</v>
+      </c>
+      <c r="G6">
+        <v>-0.7187756622190594</v>
+      </c>
+      <c r="H6">
+        <v>0.4722791555842796</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B7">
-        <v>-6.33143121329404</v>
+        <v>-0.3940235991861403</v>
       </c>
       <c r="C7">
-        <v>16.46944561421859</v>
+        <v>13.24540892556356</v>
       </c>
       <c r="D7">
-        <v>-0.3844349932354686</v>
+        <v>-0.02974793767413833</v>
       </c>
       <c r="E7">
-        <v>0.7006560685929735</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>0.9762680800857526</v>
+      </c>
+      <c r="F7">
+        <v>11.1026240647563</v>
+      </c>
+      <c r="G7">
+        <v>-0.03548923181474837</v>
+      </c>
+      <c r="H7">
+        <v>0.9716896327348288</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B8">
-        <v>0.0167359774052744</v>
+        <v>0.0366401108732437</v>
       </c>
       <c r="C8">
-        <v>0.05088428775097745</v>
+        <v>0.04732560816956701</v>
       </c>
       <c r="D8">
-        <v>0.3289026563008719</v>
+        <v>0.7742132069800917</v>
       </c>
       <c r="E8">
-        <v>0.7422292664823107</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>0.4388047194599856</v>
+      </c>
+      <c r="F8">
+        <v>0.04523758918602049</v>
+      </c>
+      <c r="G8">
+        <v>0.8099483534053222</v>
+      </c>
+      <c r="H8">
+        <v>0.4179698596139714</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B9">
-        <v>1.092645959019132</v>
+        <v>1.586810016707245</v>
       </c>
       <c r="C9">
-        <v>0.5186626339015583</v>
+        <v>0.4416598313222467</v>
       </c>
       <c r="D9">
-        <v>2.106660259675685</v>
+        <v>3.592832999905456</v>
       </c>
       <c r="E9">
-        <v>0.03514703928400031</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>0.0003271022367909993</v>
+      </c>
+      <c r="F9">
+        <v>0.4018009168046406</v>
+      </c>
+      <c r="G9">
+        <v>3.949244390297813</v>
+      </c>
+      <c r="H9">
+        <v>7.839827797329058E-05</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B10">
-        <v>0.03613721902295142</v>
+        <v>-0.03861899092096621</v>
       </c>
       <c r="C10">
-        <v>0.0595317162713904</v>
+        <v>0.04113118353130785</v>
       </c>
       <c r="D10">
-        <v>0.6070246464625807</v>
+        <v>-0.9389224331843156</v>
       </c>
       <c r="E10">
-        <v>0.5438345558910298</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>0.3477705705104415</v>
+      </c>
+      <c r="F10">
+        <v>0.03562832559790837</v>
+      </c>
+      <c r="G10">
+        <v>-1.083940664425538</v>
+      </c>
+      <c r="H10">
+        <v>0.2783911081231139</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B11">
-        <v>-5.836600057749793</v>
+        <v>-7.03383372148544</v>
       </c>
       <c r="C11">
-        <v>2.316518337902262</v>
+        <v>2.110132736613461</v>
       </c>
       <c r="D11">
-        <v>-2.51955702756714</v>
+        <v>-3.333360787897161</v>
       </c>
       <c r="E11">
-        <v>0.01175026046662819</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>0.0008580359850742791</v>
+      </c>
+      <c r="F11">
+        <v>2.166932991518218</v>
+      </c>
+      <c r="G11">
+        <v>-3.245985800676433</v>
+      </c>
+      <c r="H11">
+        <v>0.001170446771807665</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B12">
-        <v>-22.38568442186786</v>
+        <v>17.38875392976117</v>
       </c>
       <c r="C12">
-        <v>40.835030109933</v>
+        <v>28.06063235820265</v>
       </c>
       <c r="D12">
-        <v>-0.5481980633197234</v>
+        <v>0.6196850344563997</v>
       </c>
       <c r="E12">
-        <v>0.5835559117747207</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>0.5354651703929549</v>
+      </c>
+      <c r="F12">
+        <v>26.72521794415738</v>
+      </c>
+      <c r="G12">
+        <v>0.6506496585395543</v>
+      </c>
+      <c r="H12">
+        <v>0.5152726667288923</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B13">
-        <v>-3.483539054918094</v>
+        <v>-3.462138940082573</v>
       </c>
       <c r="C13">
-        <v>0.1439103124885331</v>
+        <v>0.1240287142893549</v>
       </c>
       <c r="D13">
-        <v>-24.20631985769376</v>
+        <v>-27.91401136357437</v>
       </c>
       <c r="E13">
         <v>0</v>
